--- a/Template_Outage_EIC_Monitoring_unit 2.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 2.xlsx
@@ -4397,8 +4397,6 @@
           <t>INSPECTION FRAME MOTOR</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>1</v>
       </c>
@@ -4417,8 +4415,6 @@
           <t>REGREASING (JIKA DILENGKAPI NIPPLE GREASE)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
         <v>1</v>
       </c>
@@ -4437,8 +4433,6 @@
           <t>INSPECTION BEARING DAN REPLACEMENT (JIKA DIPERLUKAN)</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
         <v>1</v>
       </c>
@@ -4457,8 +4451,6 @@
           <t>INSPECTION TAHANAN ISOLASI</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="b">
         <v>1</v>
       </c>
@@ -4477,8 +4469,6 @@
           <t>INSPECTION TAHANAN WINDING</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="b">
         <v>1</v>
       </c>
@@ -4497,8 +4487,6 @@
           <t>INSPECTION COOLING FAN</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="b">
         <v>1</v>
       </c>
@@ -4517,8 +4505,6 @@
           <t>INSPECTION TERMINASI</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="b">
         <v>1</v>
       </c>
@@ -4537,8 +4523,6 @@
           <t>INSPECTION KONEKSI GROUNDING SYSTEM</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="b">
         <v>1</v>
       </c>
@@ -4557,8 +4541,6 @@
           <t>INSPECTION AND CALIBRATION MEASUREMENT DEVICE</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
         <v>1</v>
       </c>
@@ -4582,7 +4564,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
         <v>1</v>
       </c>
@@ -4606,7 +4587,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
         <v>1</v>
       </c>
@@ -4630,7 +4610,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="b">
         <v>1</v>
       </c>
@@ -4654,7 +4633,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="b">
         <v>1</v>
       </c>
@@ -4678,7 +4656,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="b">
         <v>1</v>
       </c>
@@ -4702,7 +4679,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="b">
         <v>1</v>
       </c>
@@ -4726,7 +4702,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="b">
         <v>1</v>
       </c>
@@ -4750,7 +4725,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
         <v>1</v>
       </c>
@@ -4774,7 +4748,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
         <v>1</v>
       </c>
@@ -4798,7 +4771,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="b">
         <v>1</v>
       </c>
@@ -4822,7 +4794,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="b">
         <v>1</v>
       </c>
@@ -4846,7 +4817,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="b">
         <v>1</v>
       </c>
@@ -4870,7 +4840,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="b">
         <v>1</v>
       </c>
@@ -4894,7 +4863,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
       <c r="E24" t="b">
         <v>1</v>
       </c>
@@ -4918,7 +4886,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
       <c r="E25" t="b">
         <v>1</v>
       </c>
@@ -4942,7 +4909,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="b">
         <v>1</v>
       </c>
@@ -4966,7 +4932,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="b">
         <v>1</v>
       </c>
@@ -4990,7 +4955,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="b">
         <v>1</v>
       </c>
@@ -5014,7 +4978,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
       <c r="E29" t="b">
         <v>1</v>
       </c>
@@ -5038,7 +5001,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
       <c r="E30" t="b">
         <v>1</v>
       </c>
@@ -5062,7 +5024,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
       <c r="E31" t="b">
         <v>1</v>
       </c>
@@ -5086,7 +5047,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
       <c r="E32" t="b">
         <v>1</v>
       </c>
@@ -5110,7 +5070,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
       <c r="E33" t="b">
         <v>1</v>
       </c>
@@ -5134,7 +5093,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="b">
         <v>1</v>
       </c>
@@ -5158,7 +5116,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="b">
         <v>1</v>
       </c>
@@ -5182,7 +5139,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
       <c r="E36" t="b">
         <v>1</v>
       </c>
@@ -5206,7 +5162,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
       <c r="E37" t="b">
         <v>1</v>
       </c>
@@ -5230,7 +5185,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
       <c r="E38" t="b">
         <v>1</v>
       </c>
@@ -5254,7 +5208,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
       <c r="E39" t="b">
         <v>1</v>
       </c>
@@ -5278,7 +5231,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
       <c r="E40" t="b">
         <v>1</v>
       </c>
@@ -5302,7 +5254,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
       <c r="E41" t="b">
         <v>1</v>
       </c>
@@ -5326,7 +5277,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
       <c r="E42" t="b">
         <v>1</v>
       </c>
@@ -5350,7 +5300,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
       <c r="E43" t="b">
         <v>1</v>
       </c>
@@ -6354,7 +6303,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
       <c r="E79" t="b">
         <v>1</v>
       </c>
@@ -6378,7 +6326,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
       <c r="E80" t="b">
         <v>1</v>
       </c>
@@ -6402,7 +6349,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
       <c r="E81" t="b">
         <v>1</v>
       </c>
@@ -6426,7 +6372,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
       <c r="E82" t="b">
         <v>1</v>
       </c>
@@ -6450,7 +6395,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="b">
         <v>1</v>
       </c>
@@ -6474,7 +6418,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
       <c r="E84" t="b">
         <v>1</v>
       </c>
@@ -6498,7 +6441,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
       <c r="E85" t="b">
         <v>1</v>
       </c>
@@ -6522,7 +6464,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
       <c r="E86" t="b">
         <v>1</v>
       </c>
@@ -6546,7 +6487,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
       <c r="E87" t="b">
         <v>1</v>
       </c>
@@ -6570,7 +6510,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
       <c r="E88" t="b">
         <v>1</v>
       </c>
@@ -6594,7 +6533,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
       <c r="E89" t="b">
         <v>1</v>
       </c>
@@ -6618,7 +6556,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr"/>
       <c r="E90" t="b">
         <v>1</v>
       </c>
@@ -6642,7 +6579,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
       <c r="E91" t="b">
         <v>1</v>
       </c>
@@ -6666,7 +6602,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
       <c r="E92" t="b">
         <v>1</v>
       </c>
@@ -6690,7 +6625,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
       <c r="E93" t="b">
         <v>1</v>
       </c>
@@ -6714,7 +6648,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="b">
         <v>1</v>
       </c>
@@ -6738,7 +6671,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
       <c r="E95" t="b">
         <v>1</v>
       </c>
@@ -6762,7 +6694,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
       <c r="E96" t="b">
         <v>1</v>
       </c>
@@ -6786,7 +6717,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
       <c r="E97" t="b">
         <v>1</v>
       </c>
@@ -6810,7 +6740,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
       <c r="E98" t="b">
         <v>1</v>
       </c>
@@ -6834,7 +6763,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr"/>
       <c r="E99" t="b">
         <v>1</v>
       </c>
@@ -6858,7 +6786,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
       <c r="E100" t="b">
         <v>1</v>
       </c>
@@ -6882,7 +6809,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="b">
         <v>1</v>
       </c>
@@ -6906,7 +6832,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr"/>
       <c r="E102" t="b">
         <v>1</v>
       </c>
@@ -6930,7 +6855,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
       <c r="E103" t="b">
         <v>1</v>
       </c>
@@ -6954,7 +6878,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
       <c r="E104" t="b">
         <v>1</v>
       </c>
@@ -6978,7 +6901,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
       <c r="E105" t="b">
         <v>1</v>
       </c>
@@ -7002,7 +6924,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="b">
         <v>1</v>
       </c>
@@ -7026,7 +6947,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
       <c r="E107" t="b">
         <v>1</v>
       </c>
@@ -7050,7 +6970,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
       <c r="E108" t="b">
         <v>1</v>
       </c>
@@ -7074,7 +6993,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
       <c r="E109" t="b">
         <v>1</v>
       </c>
@@ -7098,7 +7016,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
       <c r="E110" t="b">
         <v>1</v>
       </c>
@@ -7122,7 +7039,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
       <c r="E111" t="b">
         <v>1</v>
       </c>
@@ -7146,7 +7062,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
       <c r="E112" t="b">
         <v>1</v>
       </c>
@@ -7170,7 +7085,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
       <c r="E113" t="b">
         <v>1</v>
       </c>
@@ -7194,7 +7108,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
       <c r="E114" t="b">
         <v>1</v>
       </c>
@@ -7218,7 +7131,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
       <c r="E115" t="b">
         <v>1</v>
       </c>
@@ -7242,7 +7154,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
       <c r="E116" t="b">
         <v>1</v>
       </c>
@@ -7266,7 +7177,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
       <c r="E117" t="b">
         <v>1</v>
       </c>
@@ -7290,7 +7200,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
       <c r="E118" t="b">
         <v>1</v>
       </c>
@@ -7314,7 +7223,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
       <c r="E119" t="b">
         <v>1</v>
       </c>
@@ -7338,7 +7246,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
       <c r="E120" t="b">
         <v>1</v>
       </c>
@@ -7362,7 +7269,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
       <c r="E121" t="b">
         <v>1</v>
       </c>
@@ -7386,7 +7292,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
       <c r="E122" t="b">
         <v>1</v>
       </c>
@@ -7410,7 +7315,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
       <c r="E123" t="b">
         <v>1</v>
       </c>
@@ -7434,7 +7338,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
       <c r="E124" t="b">
         <v>1</v>
       </c>
@@ -7458,7 +7361,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
       <c r="E125" t="b">
         <v>1</v>
       </c>
@@ -7482,7 +7384,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
       <c r="E126" t="b">
         <v>1</v>
       </c>
@@ -7506,7 +7407,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
       <c r="E127" t="b">
         <v>1</v>
       </c>
@@ -7530,7 +7430,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
       <c r="E128" t="b">
         <v>1</v>
       </c>
@@ -7554,7 +7453,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
       <c r="E129" t="b">
         <v>1</v>
       </c>
@@ -7578,7 +7476,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
       <c r="E130" t="b">
         <v>1</v>
       </c>
@@ -7602,7 +7499,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
       <c r="E131" t="b">
         <v>1</v>
       </c>
@@ -7626,7 +7522,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
       <c r="E132" t="b">
         <v>1</v>
       </c>
@@ -7650,7 +7545,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr"/>
       <c r="E133" t="b">
         <v>1</v>
       </c>
@@ -7674,7 +7568,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
       <c r="E134" t="b">
         <v>1</v>
       </c>
@@ -7698,7 +7591,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
       <c r="E135" t="b">
         <v>1</v>
       </c>
@@ -7722,7 +7614,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
       <c r="E136" t="b">
         <v>1</v>
       </c>
@@ -7746,7 +7637,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
       <c r="E137" t="b">
         <v>1</v>
       </c>
@@ -7770,7 +7660,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
       <c r="E138" t="b">
         <v>1</v>
       </c>
@@ -7794,7 +7683,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
       <c r="E139" t="b">
         <v>1</v>
       </c>
@@ -7818,7 +7706,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
       <c r="E140" t="b">
         <v>1</v>
       </c>
@@ -7842,7 +7729,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
       <c r="E141" t="b">
         <v>1</v>
       </c>
@@ -7866,7 +7752,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
       <c r="E142" t="b">
         <v>1</v>
       </c>
@@ -7890,7 +7775,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
       <c r="E143" t="b">
         <v>1</v>
       </c>
@@ -7914,7 +7798,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
       <c r="E144" t="b">
         <v>1</v>
       </c>
@@ -7938,7 +7821,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
       <c r="E145" t="b">
         <v>1</v>
       </c>
@@ -7962,7 +7844,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
       <c r="E146" t="b">
         <v>1</v>
       </c>
@@ -7986,7 +7867,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
       <c r="E147" t="b">
         <v>1</v>
       </c>
@@ -8010,7 +7890,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
       <c r="E148" t="b">
         <v>1</v>
       </c>
@@ -8034,7 +7913,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D149" t="inlineStr"/>
       <c r="E149" t="b">
         <v>1</v>
       </c>
@@ -8058,7 +7936,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr"/>
       <c r="E150" t="b">
         <v>1</v>
       </c>
@@ -8082,7 +7959,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr"/>
       <c r="E151" t="b">
         <v>1</v>
       </c>
@@ -8106,7 +7982,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
       <c r="E152" t="b">
         <v>1</v>
       </c>
@@ -8130,7 +8005,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
       <c r="E153" t="b">
         <v>1</v>
       </c>
@@ -8154,7 +8028,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
       <c r="E154" t="b">
         <v>1</v>
       </c>
@@ -8178,7 +8051,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
       <c r="E155" t="b">
         <v>1</v>
       </c>
@@ -8202,7 +8074,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
       <c r="E156" t="b">
         <v>1</v>
       </c>
@@ -8226,7 +8097,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
       <c r="E157" t="b">
         <v>1</v>
       </c>
@@ -8250,7 +8120,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
       <c r="E158" t="b">
         <v>1</v>
       </c>
@@ -8302,7 +8171,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
       <c r="E160" t="b">
         <v>1</v>
       </c>
@@ -8326,7 +8194,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr"/>
       <c r="E161" t="b">
         <v>1</v>
       </c>
@@ -8350,7 +8217,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
       <c r="E162" t="b">
         <v>1</v>
       </c>
@@ -8374,7 +8240,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
       <c r="E163" t="b">
         <v>1</v>
       </c>
@@ -8398,7 +8263,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
       <c r="E164" t="b">
         <v>1</v>
       </c>
@@ -8422,7 +8286,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
       <c r="E165" t="b">
         <v>1</v>
       </c>
@@ -8446,7 +8309,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
       <c r="E166" t="b">
         <v>1</v>
       </c>
@@ -8470,7 +8332,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D167" t="inlineStr"/>
       <c r="E167" t="b">
         <v>1</v>
       </c>
@@ -8494,7 +8355,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
       <c r="E168" t="b">
         <v>1</v>
       </c>
@@ -8518,7 +8378,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
       <c r="E169" t="b">
         <v>1</v>
       </c>
@@ -8542,7 +8401,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
       <c r="E170" t="b">
         <v>1</v>
       </c>
@@ -8566,7 +8424,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D171" t="inlineStr"/>
       <c r="E171" t="b">
         <v>1</v>
       </c>
@@ -8590,7 +8447,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
       <c r="E172" t="b">
         <v>1</v>
       </c>
@@ -8614,7 +8470,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
       <c r="E173" t="b">
         <v>1</v>
       </c>
@@ -8638,7 +8493,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
       <c r="E174" t="b">
         <v>1</v>
       </c>
@@ -8662,7 +8516,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
       <c r="E175" t="b">
         <v>1</v>
       </c>
@@ -8686,7 +8539,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
       <c r="E176" t="b">
         <v>1</v>
       </c>
@@ -8710,7 +8562,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
       <c r="E177" t="b">
         <v>1</v>
       </c>
@@ -8734,7 +8585,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
       <c r="E178" t="b">
         <v>1</v>
       </c>
@@ -8758,7 +8608,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
       <c r="E179" t="b">
         <v>1</v>
       </c>
@@ -8782,7 +8631,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
       <c r="E180" t="b">
         <v>1</v>
       </c>
@@ -8806,7 +8654,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
       <c r="E181" t="b">
         <v>1</v>
       </c>
@@ -8830,7 +8677,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr"/>
       <c r="E182" t="b">
         <v>1</v>
       </c>
@@ -8854,7 +8700,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
       <c r="E183" t="b">
         <v>1</v>
       </c>
@@ -8878,7 +8723,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
       <c r="E184" t="b">
         <v>1</v>
       </c>
@@ -8902,7 +8746,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
       <c r="E185" t="b">
         <v>1</v>
       </c>
@@ -8926,7 +8769,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
       <c r="E186" t="b">
         <v>1</v>
       </c>
@@ -8950,7 +8792,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
       <c r="E187" t="b">
         <v>1</v>
       </c>
@@ -8974,7 +8815,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
       <c r="E188" t="b">
         <v>1</v>
       </c>
@@ -8998,7 +8838,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
       <c r="E189" t="b">
         <v>1</v>
       </c>
@@ -9022,7 +8861,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
       <c r="E190" t="b">
         <v>1</v>
       </c>
@@ -9046,7 +8884,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
       <c r="E191" t="b">
         <v>1</v>
       </c>
@@ -9070,7 +8907,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
       <c r="E192" t="b">
         <v>1</v>
       </c>
@@ -9094,7 +8930,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
       <c r="E193" t="b">
         <v>1</v>
       </c>
@@ -9118,7 +8953,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
       <c r="E194" t="b">
         <v>1</v>
       </c>
@@ -9142,7 +8976,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D195" t="inlineStr"/>
       <c r="E195" t="b">
         <v>1</v>
       </c>
@@ -9166,7 +8999,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D196" t="inlineStr"/>
       <c r="E196" t="b">
         <v>1</v>
       </c>
@@ -9190,7 +9022,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
       <c r="E197" t="b">
         <v>1</v>
       </c>
@@ -9270,7 +9101,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
       <c r="E200" t="b">
         <v>1</v>
       </c>
@@ -9294,7 +9124,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
       <c r="E201" t="b">
         <v>1</v>
       </c>
@@ -9318,7 +9147,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
       <c r="E202" t="b">
         <v>1</v>
       </c>
@@ -9342,7 +9170,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
       <c r="E203" t="b">
         <v>1</v>
       </c>
@@ -9366,7 +9193,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
       <c r="E204" t="b">
         <v>1</v>
       </c>
@@ -9390,7 +9216,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D205" t="inlineStr"/>
       <c r="E205" t="b">
         <v>1</v>
       </c>
@@ -9414,7 +9239,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
       <c r="E206" t="b">
         <v>1</v>
       </c>
@@ -11426,7 +11250,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D278" t="inlineStr"/>
       <c r="E278" t="b">
         <v>1</v>
       </c>
@@ -11450,7 +11273,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D279" t="inlineStr"/>
       <c r="E279" t="b">
         <v>1</v>
       </c>
@@ -11474,7 +11296,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D280" t="inlineStr"/>
       <c r="E280" t="b">
         <v>1</v>
       </c>
@@ -11498,7 +11319,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr"/>
       <c r="E281" t="b">
         <v>1</v>
       </c>
@@ -11634,7 +11454,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
       <c r="E286" t="b">
         <v>1</v>
       </c>
@@ -11658,7 +11477,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
       <c r="E287" t="b">
         <v>1</v>
       </c>
@@ -11682,7 +11500,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
       <c r="E288" t="b">
         <v>1</v>
       </c>
@@ -11706,7 +11523,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
       <c r="E289" t="b">
         <v>1</v>
       </c>
@@ -11730,7 +11546,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
       <c r="E290" t="b">
         <v>1</v>
       </c>
@@ -11754,7 +11569,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
       <c r="E291" t="b">
         <v>1</v>
       </c>
@@ -11778,7 +11592,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
       <c r="E292" t="b">
         <v>1</v>
       </c>
@@ -11802,7 +11615,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
       <c r="E293" t="b">
         <v>1</v>
       </c>
@@ -11826,7 +11638,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
       <c r="E294" t="b">
         <v>1</v>
       </c>
@@ -11850,7 +11661,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
       <c r="E295" t="b">
         <v>1</v>
       </c>
@@ -11874,7 +11684,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
       <c r="E296" t="b">
         <v>1</v>
       </c>
@@ -11898,7 +11707,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
       <c r="E297" t="b">
         <v>1</v>
       </c>
@@ -11922,7 +11730,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D298" t="inlineStr"/>
       <c r="E298" t="b">
         <v>1</v>
       </c>
@@ -11946,7 +11753,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
       <c r="E299" t="b">
         <v>1</v>
       </c>
@@ -11970,7 +11776,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
       <c r="E300" t="b">
         <v>1</v>
       </c>
@@ -11994,7 +11799,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D301" t="inlineStr"/>
       <c r="E301" t="b">
         <v>1</v>
       </c>
@@ -12018,7 +11822,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
       <c r="E302" t="b">
         <v>1</v>
       </c>
@@ -12042,7 +11845,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
       <c r="E303" t="b">
         <v>1</v>
       </c>
@@ -12066,7 +11868,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
       <c r="E304" t="b">
         <v>1</v>
       </c>
@@ -12090,7 +11891,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
       <c r="E305" t="b">
         <v>1</v>
       </c>
@@ -12114,7 +11914,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
       <c r="E306" t="b">
         <v>1</v>
       </c>
@@ -12138,7 +11937,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
       <c r="E307" t="b">
         <v>1</v>
       </c>
@@ -12162,7 +11960,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D308" t="inlineStr"/>
       <c r="E308" t="b">
         <v>1</v>
       </c>
@@ -12186,7 +11983,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D309" t="inlineStr"/>
       <c r="E309" t="b">
         <v>1</v>
       </c>
@@ -12210,7 +12006,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D310" t="inlineStr"/>
       <c r="E310" t="b">
         <v>1</v>
       </c>
@@ -12234,7 +12029,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D311" t="inlineStr"/>
       <c r="E311" t="b">
         <v>1</v>
       </c>
@@ -12258,7 +12052,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
       <c r="E312" t="b">
         <v>1</v>
       </c>
@@ -12282,7 +12075,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D313" t="inlineStr"/>
       <c r="E313" t="b">
         <v>1</v>
       </c>
@@ -12306,7 +12098,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D314" t="inlineStr"/>
       <c r="E314" t="b">
         <v>1</v>
       </c>
@@ -12330,7 +12121,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D315" t="inlineStr"/>
       <c r="E315" t="b">
         <v>1</v>
       </c>
@@ -14566,7 +14356,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D395" t="inlineStr"/>
       <c r="E395" t="b">
         <v>1</v>
       </c>
@@ -14590,7 +14379,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr"/>
       <c r="E396" t="b">
         <v>1</v>
       </c>
@@ -14614,7 +14402,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
       <c r="E397" t="b">
         <v>1</v>
       </c>
@@ -14638,7 +14425,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D398" t="inlineStr"/>
       <c r="E398" t="b">
         <v>1</v>
       </c>
@@ -14662,7 +14448,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D399" t="inlineStr"/>
       <c r="E399" t="b">
         <v>1</v>
       </c>
@@ -14686,7 +14471,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D400" t="inlineStr"/>
       <c r="E400" t="b">
         <v>1</v>
       </c>
@@ -14710,7 +14494,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr"/>
       <c r="E401" t="b">
         <v>1</v>
       </c>
@@ -14734,7 +14517,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D402" t="inlineStr"/>
       <c r="E402" t="b">
         <v>1</v>
       </c>
@@ -14758,7 +14540,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D403" t="inlineStr"/>
       <c r="E403" t="b">
         <v>1</v>
       </c>
@@ -14782,7 +14563,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D404" t="inlineStr"/>
       <c r="E404" t="b">
         <v>1</v>
       </c>
@@ -14806,7 +14586,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
       <c r="E405" t="b">
         <v>1</v>
       </c>
@@ -14830,7 +14609,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D406" t="inlineStr"/>
       <c r="E406" t="b">
         <v>1</v>
       </c>
@@ -14854,7 +14632,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr"/>
       <c r="E407" t="b">
         <v>1</v>
       </c>
@@ -14878,7 +14655,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
       <c r="E408" t="b">
         <v>1</v>
       </c>
@@ -14902,7 +14678,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D409" t="inlineStr"/>
       <c r="E409" t="b">
         <v>1</v>
       </c>
@@ -14926,7 +14701,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D410" t="inlineStr"/>
       <c r="E410" t="b">
         <v>1</v>
       </c>
@@ -14950,7 +14724,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D411" t="inlineStr"/>
       <c r="E411" t="b">
         <v>1</v>
       </c>
@@ -14974,7 +14747,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D412" t="inlineStr"/>
       <c r="E412" t="b">
         <v>1</v>
       </c>
@@ -14998,7 +14770,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D413" t="inlineStr"/>
       <c r="E413" t="b">
         <v>1</v>
       </c>
@@ -15022,7 +14793,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr"/>
       <c r="E414" t="b">
         <v>1</v>
       </c>
@@ -15046,7 +14816,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
       <c r="E415" t="b">
         <v>1</v>
       </c>
@@ -15070,7 +14839,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D416" t="inlineStr"/>
       <c r="E416" t="b">
         <v>1</v>
       </c>
@@ -15094,7 +14862,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D417" t="inlineStr"/>
       <c r="E417" t="b">
         <v>1</v>
       </c>
@@ -15118,7 +14885,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D418" t="inlineStr"/>
       <c r="E418" t="b">
         <v>1</v>
       </c>
@@ -15142,7 +14908,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
       <c r="E419" t="b">
         <v>1</v>
       </c>
@@ -15166,7 +14931,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D420" t="inlineStr"/>
       <c r="E420" t="b">
         <v>1</v>
       </c>
@@ -15190,7 +14954,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
       <c r="E421" t="b">
         <v>1</v>
       </c>
@@ -15214,7 +14977,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
       <c r="E422" t="b">
         <v>1</v>
       </c>
@@ -15238,7 +15000,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D423" t="inlineStr"/>
       <c r="E423" t="b">
         <v>1</v>
       </c>
@@ -15262,7 +15023,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
       <c r="E424" t="b">
         <v>1</v>
       </c>
@@ -15286,7 +15046,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D425" t="inlineStr"/>
       <c r="E425" t="b">
         <v>1</v>
       </c>
@@ -15310,7 +15069,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
       <c r="E426" t="b">
         <v>1</v>
       </c>
@@ -15334,7 +15092,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
       <c r="E427" t="b">
         <v>1</v>
       </c>
@@ -15358,7 +15115,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D428" t="inlineStr"/>
       <c r="E428" t="b">
         <v>1</v>
       </c>
@@ -15382,7 +15138,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D429" t="inlineStr"/>
       <c r="E429" t="b">
         <v>1</v>
       </c>
@@ -15406,7 +15161,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D430" t="inlineStr"/>
       <c r="E430" t="b">
         <v>1</v>
       </c>
@@ -15430,7 +15184,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D431" t="inlineStr"/>
       <c r="E431" t="b">
         <v>1</v>
       </c>
@@ -15454,7 +15207,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D432" t="inlineStr"/>
       <c r="E432" t="b">
         <v>1</v>
       </c>
@@ -15478,7 +15230,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
       <c r="E433" t="b">
         <v>1</v>
       </c>
@@ -15502,7 +15253,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr"/>
       <c r="E434" t="b">
         <v>1</v>
       </c>
@@ -15526,7 +15276,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D435" t="inlineStr"/>
       <c r="E435" t="b">
         <v>1</v>
       </c>
@@ -15550,7 +15299,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D436" t="inlineStr"/>
       <c r="E436" t="b">
         <v>1</v>
       </c>
@@ -15574,7 +15322,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D437" t="inlineStr"/>
       <c r="E437" t="b">
         <v>1</v>
       </c>
@@ -15598,7 +15345,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D438" t="inlineStr"/>
       <c r="E438" t="b">
         <v>1</v>
       </c>
@@ -15622,7 +15368,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D439" t="inlineStr"/>
       <c r="E439" t="b">
         <v>1</v>
       </c>
@@ -15646,7 +15391,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
       <c r="E440" t="b">
         <v>1</v>
       </c>
@@ -15670,7 +15414,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr"/>
       <c r="E441" t="b">
         <v>1</v>
       </c>
@@ -15694,7 +15437,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
       <c r="E442" t="b">
         <v>1</v>
       </c>
@@ -15718,7 +15460,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D443" t="inlineStr"/>
       <c r="E443" t="b">
         <v>1</v>
       </c>
@@ -15742,7 +15483,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D444" t="inlineStr"/>
       <c r="E444" t="b">
         <v>1</v>
       </c>
@@ -15766,7 +15506,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
       <c r="E445" t="b">
         <v>1</v>
       </c>
@@ -15790,7 +15529,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
       <c r="E446" t="b">
         <v>1</v>
       </c>
@@ -15814,7 +15552,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D447" t="inlineStr"/>
       <c r="E447" t="b">
         <v>1</v>
       </c>
@@ -15838,7 +15575,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D448" t="inlineStr"/>
       <c r="E448" t="b">
         <v>1</v>
       </c>
@@ -15862,7 +15598,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
       <c r="E449" t="b">
         <v>1</v>
       </c>
@@ -15886,7 +15621,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
       <c r="E450" t="b">
         <v>1</v>
       </c>
@@ -15910,7 +15644,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D451" t="inlineStr"/>
       <c r="E451" t="b">
         <v>1</v>
       </c>
@@ -15934,7 +15667,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D452" t="inlineStr"/>
       <c r="E452" t="b">
         <v>1</v>
       </c>
@@ -15958,7 +15690,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D453" t="inlineStr"/>
       <c r="E453" t="b">
         <v>1</v>
       </c>
@@ -15982,7 +15713,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr"/>
       <c r="E454" t="b">
         <v>1</v>
       </c>
@@ -16006,7 +15736,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
       <c r="E455" t="b">
         <v>1</v>
       </c>
@@ -16030,7 +15759,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D456" t="inlineStr"/>
       <c r="E456" t="b">
         <v>1</v>
       </c>
@@ -16054,7 +15782,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D457" t="inlineStr"/>
       <c r="E457" t="b">
         <v>1</v>
       </c>
@@ -16078,7 +15805,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D458" t="inlineStr"/>
       <c r="E458" t="b">
         <v>1</v>
       </c>
@@ -16102,7 +15828,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D459" t="inlineStr"/>
       <c r="E459" t="b">
         <v>1</v>
       </c>
@@ -16126,7 +15851,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D460" t="inlineStr"/>
       <c r="E460" t="b">
         <v>1</v>
       </c>
@@ -16150,7 +15874,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D461" t="inlineStr"/>
       <c r="E461" t="b">
         <v>1</v>
       </c>
@@ -16174,7 +15897,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr"/>
       <c r="E462" t="b">
         <v>1</v>
       </c>
@@ -16198,7 +15920,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D463" t="inlineStr"/>
       <c r="E463" t="b">
         <v>1</v>
       </c>
@@ -16222,7 +15943,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D464" t="inlineStr"/>
       <c r="E464" t="b">
         <v>1</v>
       </c>
@@ -16246,7 +15966,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D465" t="inlineStr"/>
       <c r="E465" t="b">
         <v>1</v>
       </c>
@@ -16270,7 +15989,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
       <c r="E466" t="b">
         <v>1</v>
       </c>
@@ -16294,7 +16012,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D467" t="inlineStr"/>
       <c r="E467" t="b">
         <v>1</v>
       </c>
@@ -16318,7 +16035,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D468" t="inlineStr"/>
       <c r="E468" t="b">
         <v>1</v>
       </c>
@@ -16342,7 +16058,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D469" t="inlineStr"/>
       <c r="E469" t="b">
         <v>1</v>
       </c>
@@ -16366,7 +16081,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D470" t="inlineStr"/>
       <c r="E470" t="b">
         <v>1</v>
       </c>
@@ -16390,7 +16104,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D471" t="inlineStr"/>
       <c r="E471" t="b">
         <v>1</v>
       </c>
@@ -16414,7 +16127,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D472" t="inlineStr"/>
       <c r="E472" t="b">
         <v>1</v>
       </c>
@@ -16438,7 +16150,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D473" t="inlineStr"/>
       <c r="E473" t="b">
         <v>1</v>
       </c>
@@ -16462,7 +16173,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D474" t="inlineStr"/>
       <c r="E474" t="b">
         <v>1</v>
       </c>
@@ -16486,7 +16196,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D475" t="inlineStr"/>
       <c r="E475" t="b">
         <v>1</v>
       </c>
@@ -16510,7 +16219,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
       <c r="E476" t="b">
         <v>1</v>
       </c>
@@ -16534,7 +16242,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D477" t="inlineStr"/>
       <c r="E477" t="b">
         <v>1</v>
       </c>
@@ -16558,7 +16265,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D478" t="inlineStr"/>
       <c r="E478" t="b">
         <v>1</v>
       </c>
@@ -16582,7 +16288,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
       <c r="E479" t="b">
         <v>1</v>
       </c>
@@ -16606,7 +16311,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr"/>
       <c r="E480" t="b">
         <v>1</v>
       </c>
@@ -16630,7 +16334,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
       <c r="E481" t="b">
         <v>1</v>
       </c>
@@ -16654,7 +16357,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D482" t="inlineStr"/>
       <c r="E482" t="b">
         <v>1</v>
       </c>
@@ -16678,7 +16380,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D483" t="inlineStr"/>
       <c r="E483" t="b">
         <v>1</v>
       </c>
@@ -16702,7 +16403,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
       <c r="E484" t="b">
         <v>1</v>
       </c>
@@ -16726,7 +16426,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
       <c r="E485" t="b">
         <v>1</v>
       </c>
@@ -16750,7 +16449,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
       <c r="E486" t="b">
         <v>1</v>
       </c>
@@ -16774,7 +16472,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D487" t="inlineStr"/>
       <c r="E487" t="b">
         <v>1</v>
       </c>
@@ -16798,7 +16495,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D488" t="inlineStr"/>
       <c r="E488" t="b">
         <v>1</v>
       </c>
@@ -16822,7 +16518,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D489" t="inlineStr"/>
       <c r="E489" t="b">
         <v>1</v>
       </c>
@@ -16846,7 +16541,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D490" t="inlineStr"/>
       <c r="E490" t="b">
         <v>1</v>
       </c>
@@ -16870,7 +16564,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D491" t="inlineStr"/>
       <c r="E491" t="b">
         <v>1</v>
       </c>
@@ -16894,7 +16587,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D492" t="inlineStr"/>
       <c r="E492" t="b">
         <v>1</v>
       </c>
@@ -16918,7 +16610,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D493" t="inlineStr"/>
       <c r="E493" t="b">
         <v>1</v>
       </c>
@@ -16942,7 +16633,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D494" t="inlineStr"/>
       <c r="E494" t="b">
         <v>1</v>
       </c>
@@ -16966,7 +16656,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D495" t="inlineStr"/>
       <c r="E495" t="b">
         <v>1</v>
       </c>
@@ -16990,7 +16679,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D496" t="inlineStr"/>
       <c r="E496" t="b">
         <v>1</v>
       </c>
@@ -17014,7 +16702,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D497" t="inlineStr"/>
       <c r="E497" t="b">
         <v>1</v>
       </c>
@@ -17038,7 +16725,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
       <c r="E498" t="b">
         <v>1</v>
       </c>
@@ -17062,7 +16748,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D499" t="inlineStr"/>
       <c r="E499" t="b">
         <v>1</v>
       </c>
@@ -17086,7 +16771,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr"/>
       <c r="E500" t="b">
         <v>1</v>
       </c>
@@ -17110,7 +16794,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D501" t="inlineStr"/>
       <c r="E501" t="b">
         <v>1</v>
       </c>
@@ -17134,7 +16817,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D502" t="inlineStr"/>
       <c r="E502" t="b">
         <v>1</v>
       </c>
@@ -17158,7 +16840,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr"/>
       <c r="E503" t="b">
         <v>1</v>
       </c>
@@ -17182,7 +16863,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D504" t="inlineStr"/>
       <c r="E504" t="b">
         <v>1</v>
       </c>
@@ -17206,7 +16886,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D505" t="inlineStr"/>
       <c r="E505" t="b">
         <v>1</v>
       </c>
@@ -17230,7 +16909,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D506" t="inlineStr"/>
       <c r="E506" t="b">
         <v>1</v>
       </c>
@@ -17254,7 +16932,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D507" t="inlineStr"/>
       <c r="E507" t="b">
         <v>1</v>
       </c>
@@ -17278,7 +16955,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D508" t="inlineStr"/>
       <c r="E508" t="b">
         <v>1</v>
       </c>
@@ -17302,7 +16978,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D509" t="inlineStr"/>
       <c r="E509" t="b">
         <v>1</v>
       </c>
@@ -17326,7 +17001,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
       <c r="E510" t="b">
         <v>1</v>
       </c>
@@ -17350,7 +17024,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D511" t="inlineStr"/>
       <c r="E511" t="b">
         <v>1</v>
       </c>
@@ -17374,7 +17047,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D512" t="inlineStr"/>
       <c r="E512" t="b">
         <v>1</v>
       </c>
@@ -17398,7 +17070,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D513" t="inlineStr"/>
       <c r="E513" t="b">
         <v>1</v>
       </c>
@@ -17422,7 +17093,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D514" t="inlineStr"/>
       <c r="E514" t="b">
         <v>1</v>
       </c>
@@ -17446,7 +17116,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D515" t="inlineStr"/>
       <c r="E515" t="b">
         <v>1</v>
       </c>
@@ -17470,7 +17139,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D516" t="inlineStr"/>
       <c r="E516" t="b">
         <v>1</v>
       </c>
@@ -17494,7 +17162,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D517" t="inlineStr"/>
       <c r="E517" t="b">
         <v>1</v>
       </c>
@@ -17518,7 +17185,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D518" t="inlineStr"/>
       <c r="E518" t="b">
         <v>1</v>
       </c>
@@ -17542,7 +17208,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
       <c r="E519" t="b">
         <v>1</v>
       </c>
@@ -17566,7 +17231,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D520" t="inlineStr"/>
       <c r="E520" t="b">
         <v>1</v>
       </c>
@@ -17590,7 +17254,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D521" t="inlineStr"/>
       <c r="E521" t="b">
         <v>1</v>
       </c>
@@ -17614,7 +17277,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D522" t="inlineStr"/>
       <c r="E522" t="b">
         <v>1</v>
       </c>
@@ -17638,7 +17300,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D523" t="inlineStr"/>
       <c r="E523" t="b">
         <v>1</v>
       </c>
@@ -17662,7 +17323,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D524" t="inlineStr"/>
       <c r="E524" t="b">
         <v>1</v>
       </c>
@@ -17686,7 +17346,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D525" t="inlineStr"/>
       <c r="E525" t="b">
         <v>1</v>
       </c>
@@ -17710,7 +17369,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D526" t="inlineStr"/>
       <c r="E526" t="b">
         <v>1</v>
       </c>
@@ -18294,7 +17952,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D547" t="inlineStr"/>
       <c r="E547" t="b">
         <v>1</v>
       </c>
@@ -18318,7 +17975,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D548" t="inlineStr"/>
       <c r="E548" t="b">
         <v>1</v>
       </c>
@@ -18342,7 +17998,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D549" t="inlineStr"/>
       <c r="E549" t="b">
         <v>1</v>
       </c>
@@ -18366,7 +18021,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D550" t="inlineStr"/>
       <c r="E550" t="b">
         <v>1</v>
       </c>
@@ -18390,7 +18044,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D551" t="inlineStr"/>
       <c r="E551" t="b">
         <v>1</v>
       </c>
@@ -18414,7 +18067,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
       <c r="E552" t="b">
         <v>1</v>
       </c>
@@ -18438,7 +18090,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D553" t="inlineStr"/>
       <c r="E553" t="b">
         <v>1</v>
       </c>
@@ -18546,7 +18197,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
       <c r="E557" t="b">
         <v>1</v>
       </c>
@@ -18654,7 +18304,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D561" t="inlineStr"/>
       <c r="E561" t="b">
         <v>1</v>
       </c>
@@ -20358,7 +20007,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D622" t="inlineStr"/>
       <c r="E622" t="b">
         <v>1</v>
       </c>
@@ -20382,7 +20030,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D623" t="inlineStr"/>
       <c r="E623" t="b">
         <v>1</v>
       </c>
@@ -20406,7 +20053,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D624" t="inlineStr"/>
       <c r="E624" t="b">
         <v>1</v>
       </c>
@@ -22334,7 +21980,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D693" t="inlineStr"/>
       <c r="E693" t="b">
         <v>1</v>
       </c>
@@ -22358,7 +22003,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D694" t="inlineStr"/>
       <c r="E694" t="b">
         <v>1</v>
       </c>
@@ -22382,7 +22026,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D695" t="inlineStr"/>
       <c r="E695" t="b">
         <v>1</v>
       </c>
@@ -22406,7 +22049,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D696" t="inlineStr"/>
       <c r="E696" t="b">
         <v>1</v>
       </c>
@@ -22430,7 +22072,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D697" t="inlineStr"/>
       <c r="E697" t="b">
         <v>1</v>
       </c>
@@ -22454,7 +22095,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D698" t="inlineStr"/>
       <c r="E698" t="b">
         <v>1</v>
       </c>
@@ -22478,7 +22118,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D699" t="inlineStr"/>
       <c r="E699" t="b">
         <v>1</v>
       </c>
@@ -22502,7 +22141,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
       <c r="E700" t="b">
         <v>1</v>
       </c>
@@ -22526,7 +22164,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D701" t="inlineStr"/>
       <c r="E701" t="b">
         <v>1</v>
       </c>
@@ -22550,7 +22187,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D702" t="inlineStr"/>
       <c r="E702" t="b">
         <v>1</v>
       </c>
@@ -22574,7 +22210,6 @@
           <t>2026-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
       <c r="E703" t="b">
         <v>1</v>
       </c>
@@ -22598,7 +22233,6 @@
           <t>2025-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D704" t="inlineStr"/>
       <c r="E704" t="b">
         <v>1</v>
       </c>
@@ -22622,7 +22256,6 @@
           <t>2025-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D705" t="inlineStr"/>
       <c r="E705" t="b">
         <v>1</v>
       </c>
@@ -22646,7 +22279,6 @@
           <t>2025-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D706" t="inlineStr"/>
       <c r="E706" t="b">
         <v>1</v>
       </c>
@@ -22670,7 +22302,6 @@
           <t>2025-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D707" t="inlineStr"/>
       <c r="E707" t="b">
         <v>1</v>
       </c>
@@ -22694,7 +22325,6 @@
           <t>2025-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D708" t="inlineStr"/>
       <c r="E708" t="b">
         <v>1</v>
       </c>
@@ -22718,7 +22348,6 @@
           <t>2025-07-21 00:00:00</t>
         </is>
       </c>
-      <c r="D709" t="inlineStr"/>
       <c r="E709" t="b">
         <v>1</v>
       </c>
@@ -22737,7 +22366,6 @@
           <t>ACTUATOR DESH-1 SPRAY WATER ISOLATION</t>
         </is>
       </c>
-      <c r="C710" t="inlineStr"/>
       <c r="D710" t="inlineStr">
         <is>
           <t>AMP</t>
@@ -22761,7 +22389,6 @@
           <t>ACTUATOR DESH-2 SPRAY WATER ISOLATION</t>
         </is>
       </c>
-      <c r="C711" t="inlineStr"/>
       <c r="D711" t="inlineStr">
         <is>
           <t>AMP</t>
@@ -22785,7 +22412,6 @@
           <t>ACTUATOR MOV OUTLET PA FAN 1</t>
         </is>
       </c>
-      <c r="C712" t="inlineStr"/>
       <c r="D712" t="inlineStr">
         <is>
           <t>AMP</t>
@@ -22809,7 +22435,6 @@
           <t>ACTUATOR MOV PA FAN 1</t>
         </is>
       </c>
-      <c r="C713" t="inlineStr"/>
       <c r="D713" t="inlineStr">
         <is>
           <t>AMP</t>
@@ -22833,7 +22458,6 @@
           <t>ACTUATOR ISOLATION STARTUP VENTING BOILER</t>
         </is>
       </c>
-      <c r="C714" t="inlineStr"/>
       <c r="D714" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -22857,7 +22481,6 @@
           <t>ACTUATOR IGV SA FAN 2 20HLB02EX001</t>
         </is>
       </c>
-      <c r="C715" t="inlineStr"/>
       <c r="D715" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -22881,7 +22504,6 @@
           <t>FLUIDIZING VALVE BED MATERIAL</t>
         </is>
       </c>
-      <c r="C716" t="inlineStr"/>
       <c r="D716" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -22905,7 +22527,6 @@
           <t>FLUIDIZING VALVE LIMESTONE 1&amp;2</t>
         </is>
       </c>
-      <c r="C717" t="inlineStr"/>
       <c r="D717" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -22929,7 +22550,6 @@
           <t>ACTUATOR STEAM DRUM VENTING ISOLATION VALVE</t>
         </is>
       </c>
-      <c r="C718" t="inlineStr"/>
       <c r="D718" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -22953,7 +22573,6 @@
           <t>ACTUATOR STEAM DRUM MOV VENTING VALVE</t>
         </is>
       </c>
-      <c r="C719" t="inlineStr"/>
       <c r="D719" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -22977,7 +22596,6 @@
           <t>ACTUATOR STEAM DRUM CBD ISOLATION VALVE</t>
         </is>
       </c>
-      <c r="C720" t="inlineStr"/>
       <c r="D720" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23001,7 +22619,6 @@
           <t>ACTUATOR STEAM DRUM MOV CBD CONTROL VALVE</t>
         </is>
       </c>
-      <c r="C721" t="inlineStr"/>
       <c r="D721" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23025,7 +22642,6 @@
           <t>ACTUATOR STEAM DRUM IBD ISOLATION VALVE</t>
         </is>
       </c>
-      <c r="C722" t="inlineStr"/>
       <c r="D722" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23049,7 +22665,6 @@
           <t>ACTUATOR STEAM DRUM MOV IBD CONTROL VALVE</t>
         </is>
       </c>
-      <c r="C723" t="inlineStr"/>
       <c r="D723" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23073,7 +22688,6 @@
           <t>ACTUATOR MOV PA FAN2</t>
         </is>
       </c>
-      <c r="C724" t="inlineStr"/>
       <c r="D724" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23097,7 +22711,6 @@
           <t>ACTUATOR MOV OUTLET SA FAN 1</t>
         </is>
       </c>
-      <c r="C725" t="inlineStr"/>
       <c r="D725" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23121,7 +22734,6 @@
           <t>ACTUATOR BYPASS SPRAY CONTROL VALVE 20LCE40AA210</t>
         </is>
       </c>
-      <c r="C726" t="inlineStr"/>
       <c r="D726" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23145,7 +22757,6 @@
           <t>CEP DISCHARGE VALVE</t>
         </is>
       </c>
-      <c r="C727" t="inlineStr"/>
       <c r="D727" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23169,7 +22780,6 @@
           <t>ACTUATOR ON/OFF NRV STEAM EXTRACTION 1, 2, 3</t>
         </is>
       </c>
-      <c r="C728" t="inlineStr"/>
       <c r="D728" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23193,7 +22803,6 @@
           <t>ACTUATOR ON/OFF VALVE CEP-1 &amp; CEP-2</t>
         </is>
       </c>
-      <c r="C729" t="inlineStr"/>
       <c r="D729" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23217,7 +22826,6 @@
           <t>ACTUATOR MOV INLET ECONOMIZER</t>
         </is>
       </c>
-      <c r="C730" t="inlineStr"/>
       <c r="D730" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23241,7 +22849,6 @@
           <t>ACTUATOR MOV RECIRCULATION ECONOMIZER</t>
         </is>
       </c>
-      <c r="C731" t="inlineStr"/>
       <c r="D731" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23265,7 +22872,6 @@
           <t>20HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
         </is>
       </c>
-      <c r="C732" t="inlineStr"/>
       <c r="D732" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23289,7 +22895,6 @@
           <t>20HAH46CT010: TEMPERATURE AFTER DESH 1</t>
         </is>
       </c>
-      <c r="C733" t="inlineStr"/>
       <c r="D733" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23313,7 +22918,6 @@
           <t>20HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
-      <c r="C734" t="inlineStr"/>
       <c r="D734" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23337,7 +22941,6 @@
           <t>20LBS10CT001: STGE EXTRACTION I TO LPH1 TEMP</t>
         </is>
       </c>
-      <c r="C735" t="inlineStr"/>
       <c r="D735" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23361,7 +22964,6 @@
           <t>20HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
-      <c r="C736" t="inlineStr"/>
       <c r="D736" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23385,7 +22987,6 @@
           <t>20HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
         </is>
       </c>
-      <c r="C737" t="inlineStr"/>
       <c r="D737" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23409,7 +23010,6 @@
           <t>20HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
         </is>
       </c>
-      <c r="C738" t="inlineStr"/>
       <c r="D738" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23433,7 +23033,6 @@
           <t>20LAC20CP101: DP SWITCH BFP 1</t>
         </is>
       </c>
-      <c r="C739" t="inlineStr"/>
       <c r="D739" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23457,7 +23056,6 @@
           <t>20LAC30CP101: DP SWITCH BFP 2</t>
         </is>
       </c>
-      <c r="C740" t="inlineStr"/>
       <c r="D740" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23481,7 +23079,6 @@
           <t>ACTUATOR DESH-1 SPRAY WATER CONTROL VALVE</t>
         </is>
       </c>
-      <c r="C741" t="inlineStr"/>
       <c r="D741" t="inlineStr">
         <is>
           <t>AMP</t>
@@ -23505,7 +23102,6 @@
           <t>MOV DISCHARGE BFP-1</t>
         </is>
       </c>
-      <c r="C742" t="inlineStr"/>
       <c r="D742" t="inlineStr">
         <is>
           <t>AMP</t>
@@ -23529,7 +23125,6 @@
           <t>SOOT BLOWER CONTROL VALVE</t>
         </is>
       </c>
-      <c r="C743" t="inlineStr"/>
       <c r="D743" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23553,7 +23148,6 @@
           <t>ACTUATOR MOV TURBINE STOP VALVE</t>
         </is>
       </c>
-      <c r="C744" t="inlineStr"/>
       <c r="D744" t="inlineStr">
         <is>
           <t>MSW</t>
@@ -23577,7 +23171,6 @@
           <t>20HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
-      <c r="C745" t="inlineStr"/>
       <c r="D745" t="inlineStr">
         <is>
           <t>JAPA</t>

--- a/Template_Outage_EIC_Monitoring_unit 2.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 2.xlsx
@@ -1304,6 +1304,11 @@
       <c r="F7" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -1357,6 +1362,11 @@
       <c r="G8" s="11" t="n">
         <v>46226</v>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -1967,6 +1977,11 @@
       <c r="F19" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2017,6 +2032,11 @@
       <c r="F20" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2341,6 +2361,11 @@
       <c r="F26" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2391,6 +2416,11 @@
       <c r="F27" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2441,6 +2471,11 @@
       <c r="F28" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2750,6 +2785,11 @@
       <c r="F34" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2853,6 +2893,11 @@
       <c r="F36" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2903,6 +2948,11 @@
       <c r="F37" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -2953,6 +3003,11 @@
       <c r="F38" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3003,6 +3058,11 @@
       <c r="F39" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3053,6 +3113,11 @@
       <c r="F40" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3103,6 +3168,11 @@
       <c r="F41" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3203,6 +3273,11 @@
       <c r="F43" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3303,6 +3378,11 @@
       <c r="F45" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3353,6 +3433,11 @@
       <c r="F46" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3403,6 +3488,11 @@
       <c r="F47" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3609,6 +3699,11 @@
       <c r="F51" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -3883,6 +3978,11 @@
       <c r="F56" s="11" t="n">
         <v>46224</v>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>FINISH</t>
@@ -4244,6 +4344,11 @@
       </c>
       <c r="F63" s="11" t="n">
         <v>46224</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -5600,7 +5705,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5628,7 +5733,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5656,7 +5761,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5964,7 +6069,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -6272,7 +6377,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6346,7 +6451,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E81" t="b">
@@ -6369,7 +6474,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E82" t="b">
@@ -6392,7 +6497,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E83" t="b">
@@ -6415,7 +6520,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E84" t="b">
@@ -6645,7 +6750,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E94" t="b">
@@ -6714,7 +6819,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E97" t="b">
@@ -6737,7 +6842,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E98" t="b">
@@ -6760,7 +6865,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E99" t="b">
@@ -6990,7 +7095,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E109" t="b">
@@ -7082,7 +7187,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E113" t="b">
@@ -7105,7 +7210,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E114" t="b">
@@ -7128,7 +7233,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E115" t="b">
@@ -7151,7 +7256,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E116" t="b">
@@ -7174,7 +7279,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E117" t="b">
@@ -7404,7 +7509,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E127" t="b">
@@ -7473,7 +7578,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E130" t="b">
@@ -7496,7 +7601,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E131" t="b">
@@ -7519,7 +7624,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E132" t="b">
@@ -7542,7 +7647,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E133" t="b">
@@ -8214,7 +8319,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E162" t="b">
@@ -8237,7 +8342,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E163" t="b">
@@ -8260,7 +8365,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E164" t="b">
@@ -8283,7 +8388,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E165" t="b">
@@ -8306,7 +8411,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E166" t="b">
@@ -8329,7 +8434,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E167" t="b">
@@ -8352,7 +8457,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E168" t="b">
@@ -8536,7 +8641,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E176" t="b">
@@ -8559,7 +8664,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E177" t="b">
@@ -8628,7 +8733,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E180" t="b">
@@ -8651,7 +8756,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E181" t="b">
@@ -8674,7 +8779,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E182" t="b">
@@ -8697,7 +8802,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E183" t="b">
@@ -8720,7 +8825,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E184" t="b">
@@ -9042,7 +9147,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -9070,7 +9175,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -11135,7 +11240,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -11163,7 +11268,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -11191,7 +11296,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -11219,7 +11324,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -11316,7 +11421,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E281" t="b">
@@ -11339,7 +11444,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -11395,7 +11500,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -14583,7 +14688,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E405" t="b">
@@ -14606,7 +14711,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E406" t="b">
@@ -14629,7 +14734,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E407" t="b">
@@ -14652,7 +14757,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E408" t="b">
@@ -14744,7 +14849,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E412" t="b">
@@ -14767,7 +14872,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E413" t="b">
@@ -14813,7 +14918,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E415" t="b">
@@ -14836,7 +14941,7 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E416" t="b">
@@ -14859,7 +14964,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E417" t="b">
@@ -14882,7 +14987,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E418" t="b">
@@ -14905,7 +15010,7 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E419" t="b">
@@ -14997,7 +15102,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E423" t="b">
@@ -15020,7 +15125,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E424" t="b">
@@ -15043,7 +15148,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E425" t="b">
@@ -15066,7 +15171,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E426" t="b">
@@ -15089,7 +15194,7 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E427" t="b">
@@ -15112,7 +15217,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E428" t="b">
@@ -15135,7 +15240,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E429" t="b">
@@ -15204,7 +15309,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E432" t="b">
@@ -15227,7 +15332,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E433" t="b">
@@ -15250,7 +15355,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E434" t="b">
@@ -15273,7 +15378,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E435" t="b">
@@ -15296,7 +15401,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E436" t="b">
@@ -15319,7 +15424,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E437" t="b">
@@ -15342,7 +15447,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E438" t="b">
@@ -15365,7 +15470,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E439" t="b">
@@ -15388,7 +15493,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E440" t="b">
@@ -15411,7 +15516,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E441" t="b">
@@ -15434,7 +15539,7 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E442" t="b">
@@ -15457,7 +15562,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E443" t="b">
@@ -15480,7 +15585,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E444" t="b">
@@ -15503,7 +15608,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E445" t="b">
@@ -15526,7 +15631,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E446" t="b">
@@ -15871,7 +15976,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E461" t="b">
@@ -15894,7 +15999,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E462" t="b">
@@ -15917,7 +16022,7 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E463" t="b">
@@ -15940,7 +16045,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E464" t="b">
@@ -15963,7 +16068,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E465" t="b">
@@ -15986,7 +16091,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E466" t="b">
@@ -16009,7 +16114,7 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E467" t="b">
@@ -16032,7 +16137,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E468" t="b">
@@ -16331,7 +16436,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E481" t="b">
@@ -16354,7 +16459,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E482" t="b">
@@ -16377,7 +16482,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E483" t="b">
@@ -16400,7 +16505,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E484" t="b">
@@ -16423,7 +16528,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E485" t="b">
@@ -16446,7 +16551,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E486" t="b">
@@ -16538,7 +16643,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E490" t="b">
@@ -16561,7 +16666,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E491" t="b">
@@ -16584,7 +16689,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E492" t="b">
@@ -16607,7 +16712,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E493" t="b">
@@ -16630,7 +16735,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E494" t="b">
@@ -16653,7 +16758,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E495" t="b">
@@ -16676,7 +16781,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E496" t="b">
@@ -16699,7 +16804,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E497" t="b">
@@ -16722,7 +16827,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E498" t="b">
@@ -16745,7 +16850,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E499" t="b">
@@ -16768,7 +16873,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E500" t="b">
@@ -16791,7 +16896,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E501" t="b">
@@ -16814,7 +16919,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E502" t="b">
@@ -16837,7 +16942,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E503" t="b">
@@ -16860,7 +16965,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E504" t="b">
@@ -16906,7 +17011,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E506" t="b">
@@ -16952,7 +17057,7 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E508" t="b">
@@ -17113,7 +17218,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E515" t="b">
@@ -17136,7 +17241,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E516" t="b">
@@ -17159,7 +17264,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E517" t="b">
@@ -17182,7 +17287,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E518" t="b">
@@ -17274,7 +17379,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E522" t="b">
@@ -17297,7 +17402,7 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E523" t="b">
@@ -17320,7 +17425,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E524" t="b">
@@ -17343,7 +17448,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E525" t="b">
@@ -17366,7 +17471,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E526" t="b">
@@ -17473,7 +17578,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -17501,7 +17606,7 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -17529,7 +17634,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -17557,7 +17662,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -17585,7 +17690,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -17613,7 +17718,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -17641,7 +17746,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -17669,7 +17774,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -17697,7 +17802,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -17725,7 +17830,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -17809,7 +17914,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -17837,7 +17942,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -17893,7 +17998,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -18324,7 +18429,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -18352,7 +18457,7 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -18380,7 +18485,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -18408,7 +18513,7 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -18436,7 +18541,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -18688,7 +18793,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -19864,7 +19969,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -19892,7 +19997,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -22000,7 +22105,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E694" t="b">
@@ -22023,7 +22128,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E695" t="b">
@@ -22115,7 +22220,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E699" t="b">
@@ -22138,7 +22243,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E700" t="b">
@@ -22161,7 +22266,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E701" t="b">
@@ -22184,7 +22289,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E702" t="b">
@@ -22207,7 +22312,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>2026-07-21 00:00:00</t>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="E703" t="b">
@@ -22872,6 +22977,11 @@
           <t>20HAH36CT0010: TEMPERATURE BEFORE DESH 2</t>
         </is>
       </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D732" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -22895,6 +23005,11 @@
           <t>20HAH46CT010: TEMPERATURE AFTER DESH 1</t>
         </is>
       </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D733" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -22918,6 +23033,11 @@
           <t>20HNA11CT001: CYCLONE OUTLET TEMPERATURE</t>
         </is>
       </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D734" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -22941,6 +23061,11 @@
           <t>20LBS10CT001: STGE EXTRACTION I TO LPH1 TEMP</t>
         </is>
       </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D735" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -22964,6 +23089,11 @@
           <t>20HJF13CP302: LDO PRESSURE LOW TRIP FOR LANCES</t>
         </is>
       </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D736" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -22987,6 +23117,11 @@
           <t>20HJF13CP303: LDO PRESSURE HIGH TRIP FOR LANCES</t>
         </is>
       </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D737" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23010,6 +23145,11 @@
           <t>20HJG89CP301: LPG GAS PRESSURE BEFORE MTV</t>
         </is>
       </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D738" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23033,6 +23173,11 @@
           <t>20LAC20CP101: DP SWITCH BFP 1</t>
         </is>
       </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D739" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23056,6 +23201,11 @@
           <t>20LAC30CP101: DP SWITCH BFP 2</t>
         </is>
       </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
+        </is>
+      </c>
       <c r="D740" t="inlineStr">
         <is>
           <t>JAPA</t>
@@ -23169,6 +23319,11 @@
       <c r="B745" t="inlineStr">
         <is>
           <t>20HJN13CP302: ATOM AIR PRESSURE LOW TRIP FOR LANCES</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>31/08/2026</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">

--- a/Template_Outage_EIC_Monitoring_unit 2.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 2.xlsx
@@ -31843,7 +31843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T34"/>
+  <dimension ref="A1:U34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -32383,12 +32383,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lance Burner</t>
+          <t>Lower Burner</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>2.5 Kg/Cm2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NC</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -32427,12 +32432,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lance Burner</t>
+          <t>Lower Burner</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>2.5 Kg/Cm2</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>NC</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -32471,12 +32481,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lance Burner</t>
+          <t>Lower Burner</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>13.0 Kg/Cm2</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">

--- a/Template_Outage_EIC_Monitoring_unit 2.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 2.xlsx
@@ -411,21 +411,21 @@
     <row r="2" ht="16.3" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">DASHBOARD RINGKASAN PROGRESS OUTAGE EIC — UNIT 1 </t>
+          <t>EIC OUTAGE PROGRESS SUMMARY DASHBOARD — UNIT 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>*Sheet ini berisi FORMULA otomatis — jangan diedit manual. Update data di sheet masing-masing.</t>
+          <t>*This sheet contains automated FORMULAS — do not edit manually. Update data in respective sheets.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>1. WORK ORDER (WorkOrder)</t>
+          <t>1. WORK ORDERS (WorkOrder)</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2. ACTUATOR VALVE (ActuatorValve)</t>
+          <t>2. ACTUATOR VALVES (ActuatorValve)</t>
         </is>
       </c>
     </row>
@@ -565,12 +565,12 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>SELESAI (WDONE)</t>
+          <t>COMPLETED (WDONE)</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>BELUM SELESAI</t>
+          <t>NOT COMPLETED</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -599,19 +599,19 @@
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>4. RINGKASAN TEMUAN (FINDINGS)</t>
+          <t>4. FINDINGS SUMMARY (FINDINGS)</t>
         </is>
       </c>
     </row>
     <row r="22" ht="38.15" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Sumber Data</t>
+          <t>Data Source</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Jumlah Baris dengan Temuan Terisi</t>
+          <t>Total Rows with Recorded Findings</t>
         </is>
       </c>
     </row>
@@ -702,14 +702,14 @@
     <row r="2" ht="16.3" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>TEMPLATE DATA — OUTAGE EIC WORK ORDER MONITORING SYSTEM</t>
+          <t>DATA TEMPLATE — OUTAGE EIC WORK ORDER MONITORING SYSTEM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>PLTU MSW — Unit 1 &amp; Unit 2</t>
+          <t>MSW POWER PLANT — Unit 1 &amp; Unit 2</t>
         </is>
       </c>
     </row>
@@ -719,98 +719,98 @@
     <row r="7">
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>PETUNJUK PENGISIAN:</t>
+          <t>INSTRUCTIONS &amp; GUIDELINES:</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>1. File ini adalah SUMBER DATA yang dibaca langsung oleh sistem web Outage EIC Monitoring.</t>
+          <t>1. This file is the primary DATA SOURCE read directly by the Outage EIC Monitoring web system.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>2. Sel dengan warna KUNING adalah kolom yang wajib diisi/diupdate manual oleh PIC di lapangan.</t>
+          <t>2. Cells highlighted in YELLOW must be manually filled/updated by field PIC personnel.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>3. Kolom 'Temuan' dan 'Tindak Lanjut' diisi bila ditemukan kondisi abnormal saat inspeksi.</t>
+          <t>3. The 'Temuan' (Findings) and 'Tindak Lanjut' (Action Taken) columns are used for abnormal conditions during inspection.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>4. Kolom 'Jumlah Foto' TIDAK perlu diisi manual — akan terisi otomatis oleh sistem web saat PIC</t>
+          <t>4. The 'Photo Count' column does NOT need manual entry — it is automatically populated by the web application</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   mengupload foto temuan melalui aplikasi (foto tersimpan di folder Finding/&lt;Nama WO atau Komponen&gt;/).</t>
+          <t xml:space="preserve">   when uploading finding photos (stored in Finding/&lt;WO or Component Name&gt;/).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>5. Sistem web dapat MEMBACA dan MENULIS langsung ke file ini — jangan mengubah nama kolom (header)</t>
+          <t>5. The web system can READ and WRITE directly to this file — do not alter column positions or structure</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   atau urutan sheet, karena parser web memetakan data berdasarkan nama header persis seperti ini.</t>
+          <t xml:space="preserve">   because web parsers map data based on this standard structure.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>6. Baris berwarna HIJAU MUDA pada tiap sheet adalah CONTOH pengisian data — hapus / timpa saat</t>
+          <t>6. Light green rows on each sheet serve as EXAMPLES — overwrite with actual outage records.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   mulai memasukkan data outage yang sebenarnya.</t>
+          <t xml:space="preserve">   when beginning actual data entry.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>7. Kolom 'Unit' diisi angka 1 atau 2 sesuai unit yang dikerjakan.</t>
+          <t>7. The 'Unit' column indicates 1 or 2 according to the operating outage unit.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>8. Untuk sheet Actuator Valve: daftar equipment (Equipment_ID &amp; Equipment_Description) SAMA untuk</t>
+          <t>8. For Actuator Valve sheet: equipment list is identical for Unit 1 and Unit 2 –</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Unit 1 dan Unit 2 — buat 2 baris per equipment (satu baris Unit=1, satu baris Unit=2) dengan</t>
+          <t xml:space="preserve">   Unit 1 and Unit 2 — maintain separate status rows per unit,</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Equipment_ID yang sama, namun kolom progress/status/temuan diisi terpisah sesuai kondisi tiap unit.</t>
+          <t xml:space="preserve">   with same Equipment_ID, but progress/status/findings tracked separately per unit.</t>
         </is>
       </c>
     </row>
@@ -820,63 +820,63 @@
     <row r="22">
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>DAFTAR SHEET:</t>
+          <t>SHEET DIRECTORY:</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - WorkOrder                 : daftar Work Order (WO) utama section EIC</t>
+          <t xml:space="preserve"> - WorkOrder                 : Master Work Orders (WO) list for EIC section</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - WorkOrder_Checklist       : rincian sub-task/checklist per WO</t>
+          <t xml:space="preserve"> - WorkOrder_Checklist       : Sub-task breakdown and checklist per WO</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - ActuatorValve             : progress actuator &amp; valve (Unit 1 &amp; 2, list sama)</t>
+          <t xml:space="preserve"> - ActuatorValve             : Actuator and valve progress monitoring (Unit 1 &amp; 2)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Instrument_PressureTX     : kalibrasi pressure &amp; flow transmitter</t>
+          <t xml:space="preserve"> - Instrument_PressureTX     : Pressure and flow transmitter calibration</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Instrument_TemperatureTX  : kalibrasi temperature transmitter</t>
+          <t xml:space="preserve"> - Instrument_TemperatureTX  : Temperature transmitter calibration</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Instrument_PressureSwitch : verifikasi &amp; kalibrasi pressure switch</t>
+          <t xml:space="preserve"> - Instrument_PressureSwitch : Pressure switch verification &amp; calibration</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - PIC_Scope_Master          : master pembagian scope kerja &amp; PIC (Vendor / MSW)</t>
+          <t xml:space="preserve"> - PIC_Scope_Master          : Job scope allocation &amp; PIC master (Vendor / MSW)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> - Dashboard_Summary         : rekap statistik otomatis (jangan diedit manual, berisi formula)</t>
+          <t xml:space="preserve"> - Dashboard_Summary         : Automated statistical summary (formula protected)</t>
         </is>
       </c>
     </row>
@@ -940,17 +940,17 @@
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>Tanggal_Schedule</t>
+          <t>Schedule_Date</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Tanggal_Actual_Start</t>
+          <t>Actual_Start_Date</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>Tanggal_Finish</t>
+          <t>Finish_Date</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>Persen_Progress</t>
+          <t>Progress_Percent</t>
         </is>
       </c>
       <c r="M1" s="10" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>Temuan</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="P1" s="10" t="inlineStr">
         <is>
-          <t>Tindak_Lanjut</t>
+          <t>Action_Taken</t>
         </is>
       </c>
       <c r="Q1" s="10" t="inlineStr">
         <is>
-          <t>Jumlah_Foto</t>
+          <t>Photo_Count</t>
         </is>
       </c>
     </row>
@@ -4462,7 +4462,7 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Tanggal</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
@@ -4472,22 +4472,22 @@
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Selesai_TRUE_FALSE</t>
+          <t>Done_TRUE_FALSE</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>Temuan</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Tindak_Lanjut</t>
+          <t>Action_Taken</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>Jumlah_Foto</t>
+          <t>Photo_Count</t>
         </is>
       </c>
     </row>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INSPECTION BEARING DAN REPLACEMENT (JIKA DIPERLUKAN)</t>
+          <t>INSPECTION BEARING And REPLACEMENT (JIKA DIPERLUKAN)</t>
         </is>
       </c>
       <c r="E4" t="b">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="E5" t="b">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="E6" t="b">
@@ -4707,7 +4707,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INSPECTION BEARING DAN REPLACEMENT (JIKA DIPERLUKAN)</t>
+          <t>INSPECTION BEARING And REPLACEMENT (JIKA DIPERLUKAN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DISSASEMBLY COVER FAN DAN COVER BEARING SISI DE DAN NDE</t>
+          <t>DISSASEMBLY COVER FAN And COVER BEARING SISI DE And NDE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN CLEANING BALL BEARING DE DAN NDE (REPLACE BEARING IF NEEDED)</t>
+          <t>INSPEKSI And CLEANING BALL BEARING DE And NDE (REPLACE BEARING IF NEEDED)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>REGREASING BEARING DAN PENGUKURAN TAHANAN ISOLASI</t>
+          <t>BEARING REGREASING AND INSULATION RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN BELITAN</t>
+          <t>WINDING RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DISSASEMBLY COVER FAN DAN COVER BEARING SISI DE DAN NDE</t>
+          <t>DISSASEMBLY COVER FAN And COVER BEARING SISI DE And NDE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN CLEANING BALL BEARING DE DAN NDE (REPLACE BEARING IF NEEDED)</t>
+          <t>INSPEKSI And CLEANING BALL BEARING DE And NDE (REPLACE BEARING IF NEEDED)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>REGREASING BEARING DAN PENGUKURAN TAHANAN ISOLASI</t>
+          <t>BEARING REGREASING AND INSULATION RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN BELITAN</t>
+          <t>WINDING RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DISSASEMBLY COVER FAN DAN COVER BEARING SISI DE DAN NDE</t>
+          <t>DISSASEMBLY COVER FAN And COVER BEARING SISI DE And NDE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN CLEANING BALL BEARING DE DAN NDE</t>
+          <t>INSPEKSI And CLEANING BALL BEARING DE And NDE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>REGREASING BEARING DAN PENGUKURAN TAHANAN ISOLASI</t>
+          <t>BEARING REGREASING AND INSULATION RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN BELITAN</t>
+          <t>WINDING RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6561,7 +6561,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>DISSASEMBLY COVER FAN DAN COVER BEARING SISI DE DAN NDE</t>
+          <t>DISSASEMBLY COVER FAN And COVER BEARING SISI DE And NDE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN CLEANING BALL BEARING DE DAN NDE</t>
+          <t>INSPEKSI And CLEANING BALL BEARING DE And NDE</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>REGREASING BEARING DAN PENGUKURAN TAHANAN ISOLASI</t>
+          <t>BEARING REGREASING AND INSULATION RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN BELITAN</t>
+          <t>WINDING RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DISSASEMBLY COVER FAN DAN COVER BEARING SISI DE DAN NDE</t>
+          <t>DISSASEMBLY COVER FAN And COVER BEARING SISI DE And NDE</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN CLEANING BALL BEARING DE DAN NDE</t>
+          <t>INSPEKSI And CLEANING BALL BEARING DE And NDE</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>REGREASING BEARING DAN PENGUKURAN TAHANAN ISOLASI</t>
+          <t>BEARING REGREASING AND INSULATION RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN BELITAN</t>
+          <t>WINDING RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>DISSASEMBLY COVER FAN DAN COVER BEARING SISI DE DAN NDE</t>
+          <t>DISSASEMBLY COVER FAN And COVER BEARING SISI DE And NDE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN CLEANING BALL BEARING DE DAN NDE</t>
+          <t>INSPEKSI And CLEANING BALL BEARING DE And NDE</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>REGREASING BEARING DAN PENGUKURAN TAHANAN ISOLASI</t>
+          <t>BEARING REGREASING AND INSULATION RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN BELITAN</t>
+          <t>WINDING RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7711,7 +7711,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -7849,7 +7849,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>PENGGANTIAN BEARING (JIKA DIPERLUKAN)</t>
+          <t>BEARING REPLACEMENT (IF NECESSARY)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>PENGGANTIAN BEARING</t>
+          <t>BEARING REPLACEMENT</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>INSPECTION BEARING DAN REPLACEMENT (JIKA DIPERLUKAN)</t>
+          <t>INSPECTION BEARING And REPLACEMENT (JIKA DIPERLUKAN)</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -10003,7 +10003,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -10535,7 +10535,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>INSPECTION BEARING DAN REPLACEMENT (JIKA DIPERLUKAN)</t>
+          <t>INSPECTION BEARING And REPLACEMENT (JIKA DIPERLUKAN)</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>TEST TAHANAN KONTAK</t>
+          <t>CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI KONTAK</t>
+          <t>INSULATION RESISTANCE INSPECTION KONTAK</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI BUS BAR</t>
+          <t>INSULATION RESISTANCE INSPECTION BUS BAR</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN MOTOR CHARGING, CLOSING DAN TRIPPING COIL</t>
+          <t>MOTOR CHARGING, CLOSING AND TRIPPING COIL RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>INDIKATOR DAN LAMPU PANEL SWITCH GEAR GCB</t>
+          <t>INDIKATOR And LAMPU PANEL SWITCH GEAR GCB</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -11873,7 +11873,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>PENGETESAN POWER DC UNTUK SUPPLY CONTROL 6,3 KV SWITCH GEAR GCB</t>
+          <t>DC POWER TESTING FOR 6.3 KV GCB SWITCHGEAR CONTROL SUPPLY</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>INSPECTION DAN CLEANING TERMINASI SWITCH GEAR GCB</t>
+          <t>INSPECTION And CLEANING TERMINASI SWITCH GEAR GCB</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -11942,7 +11942,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>INSPECTION DAN PENGUJIAN RELAY PROTEKSI SWITCH GEAR GCB</t>
+          <t>INSPECTION AND PROTECTION RELAY TESTING FOR GCB SWITCHGEAR</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI BUS BAR SWITCH GEAR GCB</t>
+          <t>INSULATION RESISTANCE INSPECTION BUS BAR SWITCH GEAR GCB</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
+          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -12633,7 +12633,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI GENERATOR</t>
+          <t>INSULATION RESISTANCE INSPECTION GENERATOR</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN RESISTOR</t>
+          <t>RESISTOR RESISTANCE MEASUREMENT</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -12885,7 +12885,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>PENGUKURAN TAHANAN ISOLASI  PERMANEN MAGNET GENERATOR (PMG)</t>
+          <t>INSULATION RESISTANCE MEASUREMENT  PERMANEN MAGNET GENERATOR (PMG)</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -13137,7 +13137,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>TEST TAHANAN ISOLASI NETRAL GROUNDING RESISTANCE (NGR)</t>
+          <t>NEUTRAL GROUNDING RESISTOR (NGR) INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
+          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -13445,7 +13445,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>INSPECTION DAN CLEANING PANEL</t>
+          <t>INSPECTION And CLEANING PANEL</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>INSPECTION KEBOCORAN MINYAK TRAFO</t>
+          <t>TRANSFORMER OIL LEAKAGE INSPECTION</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PROTECTIVE DEVICE TEST DAN RESET TRAFO</t>
+          <t>PROTECTIVE DEVICE TEST AND TRANSFORMER RESET</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI WINDING TRAFO</t>
+          <t>TRANSFORMER WINDING INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -13921,7 +13921,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
+          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 20MAV40CP001</t>
+          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 20MAV40CP001</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -17601,7 +17601,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 20MAV40CP002</t>
+          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 20MAV40CP002</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>INSPEKSI DAN KALIBRASI LUB OIL PRESSURE TRANSMITTER 20MAV40CP003</t>
+          <t>INSPECTION AND CALIBRATION LUB OIL PRESSURE TRANSMITTER 20MAV40CP003</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>MSW20MAJ10-M102 : UNIT 2 VACUUM PUMP A MOTOR  (MEGGER, INSPEKSI TERMINAL BLOK, DAN SISTEM COOLING MOTOR)</t>
+          <t>MSW20MAJ10-M102 : UNIT 2 VACUUM PUMP A MOTOR  (MEGGER, INSPEKSI TERMINAL BLOK, And SISTEM COOLING MOTOR)</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -18317,7 +18317,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>MSW20MAJ10-M202  : UNIT 2 VACUUM PUMP B MOTOR  (MEGGER, INSPEKSI TERMINAL BLOK, DAN SISTEM COOLING MOTOR)</t>
+          <t>MSW20MAJ10-M202  : UNIT 2 VACUUM PUMP B MOTOR  (MEGGER, INSPEKSI TERMINAL BLOK, And SISTEM COOLING MOTOR)</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -18620,7 +18620,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -18676,7 +18676,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
@@ -18956,7 +18956,7 @@
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN ISOLASI</t>
+          <t>INSULATION RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>INSPECTION TAHANAN WINDING</t>
+          <t>WINDING RESISTANCE INSPECTION</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI FREQUENCY</t>
+          <t>FREQUENCY PROTECTION TEST</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
@@ -19180,7 +19180,7 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI DIFFERENSIAL GENERATOR</t>
+          <t>GENERATOR DIFFERENTIAL PROTECTION TEST</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
@@ -19208,7 +19208,7 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI SHORT CIRCUIT</t>
+          <t>SHORT CIRCUIT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVERCURRENT</t>
+          <t>OVERCURRENT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVERVOLTAGE</t>
+          <t>OVERVOLTAGE PROTECTION TEST</t>
         </is>
       </c>
       <c r="C592" t="inlineStr">
@@ -19292,7 +19292,7 @@
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI ROTOR EARTH FAULT</t>
+          <t>ROTOR EARTH FAULT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
@@ -19320,7 +19320,7 @@
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI STATOR EARTH FAULT</t>
+          <t>STATOR EARTH FAULT PROTECTION TEST</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
@@ -19348,7 +19348,7 @@
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI REVERSE POWER</t>
+          <t>REVERSE POWER PROTECTION TEST</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
@@ -19376,7 +19376,7 @@
       </c>
       <c r="B596" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI UNDER EXCITATION</t>
+          <t>UNDER EXCITATION PROTECTION TEST</t>
         </is>
       </c>
       <c r="C596" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVER EXCITATION</t>
+          <t>OVER EXCITATION PROTECTION TEST</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI NEGATIVE SEQUENCE</t>
+          <t>NEGATIVE SEQUENCE PROTECTION TEST</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
@@ -19460,7 +19460,7 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>PENGUJIAN PROTEKSI OVERLOAD</t>
+          <t>OVERLOAD PROTECTION TEST</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>CLEANING DAN TIGHTNING</t>
+          <t>CLEANING AND TIGHTENING</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
@@ -20313,7 +20313,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR *)sudah termasuk busbar dan busduct</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST *)including busbar and busduct</t>
         </is>
       </c>
       <c r="C630" t="inlineStr">
@@ -20341,7 +20341,7 @@
       </c>
       <c r="B631" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C631" t="inlineStr">
@@ -20537,7 +20537,7 @@
       </c>
       <c r="B638" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSDUCT BUSTIE</t>
+          <t>BUSTIE BUSDUCT CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C638" t="inlineStr">
@@ -20593,7 +20593,7 @@
       </c>
       <c r="B640" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMMING</t>
+          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C640" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="B641" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB INCOMMING</t>
+          <t>INCOMING ACB CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C641" t="inlineStr">
@@ -20649,7 +20649,7 @@
       </c>
       <c r="B642" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB</t>
+          <t>CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C642" t="inlineStr">
@@ -20705,7 +20705,7 @@
       </c>
       <c r="B644" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB ESP FEEDER</t>
+          <t>ESP FEEDER ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C644" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="B645" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB ESP FEEDER</t>
+          <t>ACB CONTACT RESISTANCE TEST ESP FEEDER</t>
         </is>
       </c>
       <c r="C645" t="inlineStr">
@@ -20761,7 +20761,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB ESP FEEDER</t>
+          <t>ESP FEEDER CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C646" t="inlineStr">
@@ -20817,7 +20817,7 @@
       </c>
       <c r="B648" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB BOILER FEEDER</t>
+          <t>ACB CONTACT RESISTANCE TEST BOILER FEEDER</t>
         </is>
       </c>
       <c r="C648" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB BOILER FEEDER</t>
+          <t>BOILER FEEDER CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C649" t="inlineStr">
@@ -20901,7 +20901,7 @@
       </c>
       <c r="B651" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB COOLING TOWER FEEDER</t>
+          <t>COOLING TOWER FEEDER ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C651" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="B652" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB COOLING TOWER FEEDER</t>
+          <t>ACB CONTACT RESISTANCE TEST COOLING TOWER FEEDER</t>
         </is>
       </c>
       <c r="C652" t="inlineStr">
@@ -20957,7 +20957,7 @@
       </c>
       <c r="B653" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB COOLING TOWER FEEDER</t>
+          <t>COOLING TOWER FEEDER CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C653" t="inlineStr">
@@ -21069,7 +21069,7 @@
       </c>
       <c r="B657" t="inlineStr">
         <is>
-          <t>CEK KEBOCORAN DAN KELEMBAPAN BUSDUCT</t>
+          <t>CHECK BUSDUCT LEAKAGE AND MOISTURE</t>
         </is>
       </c>
       <c r="C657" t="inlineStr">
@@ -21237,7 +21237,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C663" t="inlineStr">
@@ -21265,7 +21265,7 @@
       </c>
       <c r="B664" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C664" t="inlineStr">
@@ -21405,7 +21405,7 @@
       </c>
       <c r="B669" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMING</t>
+          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C669" t="inlineStr">
@@ -21433,7 +21433,7 @@
       </c>
       <c r="B670" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB</t>
+          <t>ACB CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C670" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="B671" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB</t>
+          <t>CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C671" t="inlineStr">
@@ -21573,7 +21573,7 @@
       </c>
       <c r="B675" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C675" t="inlineStr">
@@ -21601,7 +21601,7 @@
       </c>
       <c r="B676" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C676" t="inlineStr">
@@ -21797,7 +21797,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI BUSBAR</t>
+          <t>BUSBAR INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C683" t="inlineStr">
@@ -21825,7 +21825,7 @@
       </c>
       <c r="B684" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK BUSBAR</t>
+          <t>BUSBAR CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C684" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="B689" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN ISOLASI ACB INCOMMING</t>
+          <t>INCOMING ACB INSULATION RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C689" t="inlineStr">
@@ -21993,7 +21993,7 @@
       </c>
       <c r="B690" t="inlineStr">
         <is>
-          <t>PENGUJIAN TAHANAN KONTAK ACB INCOMMING</t>
+          <t>INCOMING ACB CONTACT RESISTANCE TEST</t>
         </is>
       </c>
       <c r="C690" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="B691" t="inlineStr">
         <is>
-          <t>PENGUJIAN ANALISA CB</t>
+          <t>CB ANALYSIS TEST</t>
         </is>
       </c>
       <c r="C691" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
-          <t>Persen_Progress</t>
+          <t>Progress_Percent</t>
         </is>
       </c>
       <c r="I1" s="10" t="inlineStr">
@@ -23429,17 +23429,17 @@
       </c>
       <c r="M1" s="10" t="inlineStr">
         <is>
-          <t>Temuan</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="N1" s="10" t="inlineStr">
         <is>
-          <t>Tindak_Lanjut</t>
+          <t>Action_Taken</t>
         </is>
       </c>
       <c r="O1" s="10" t="inlineStr">
         <is>
-          <t>Jumlah_Foto</t>
+          <t>Photo_Count</t>
         </is>
       </c>
     </row>
@@ -24675,7 +24675,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>ada kebocoran pada shaft silinder sehingga mempengaruhi pada saat Open</t>
+          <t>Leakage on cylinder shaft affecting valve opening</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -24727,7 +24727,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Shaft silinder berat pada saat start open dari 0%-25%</t>
+          <t>Cylinder shaft heavy during initial opening from 0%-25%</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -25926,7 +25926,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Ada kebocoran pada Seal Shaft &amp; Air lock relay</t>
+          <t>Leakage found on Shaft Seal &amp; Air lock relay</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -26025,7 +26025,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Pada Seal shaft juga ditemukan kebocoran--&gt;Belum bisa diaction</t>
+          <t>Leakage also found on shaft seal--&gt;Pending action</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>-Diagfram, york &amp; accesories tdk ada kebocoran, Connector ada beberapa yg bocor--&gt;Resealing (OK).</t>
+          <t>-Diaphragm, yoke &amp; accessories no leakage, several connectors leaking--&gt;Resealedg (OK).</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -26448,7 +26448,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Air Regulator Valve no. 4 sdh diganti baru.</t>
+          <t>Air Regulator Valve no. 4 replaced with new unit.</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -27633,7 +27633,7 @@
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
-          <t>Tanggal</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="H1" s="10" t="inlineStr">
@@ -27648,17 +27648,17 @@
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>Temuan</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>Tindak_Lanjut</t>
+          <t>Action_Taken</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>Jumlah_Foto</t>
+          <t>Photo_Count</t>
         </is>
       </c>
     </row>
@@ -30729,17 +30729,17 @@
       </c>
       <c r="J1" s="10" t="inlineStr">
         <is>
-          <t>Temuan</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="K1" s="10" t="inlineStr">
         <is>
-          <t>Tindak_Lanjut</t>
+          <t>Action_Taken</t>
         </is>
       </c>
       <c r="L1" s="10" t="inlineStr">
         <is>
-          <t>Jumlah_Foto</t>
+          <t>Photo_Count</t>
         </is>
       </c>
     </row>
@@ -31843,7 +31843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U34"/>
+  <dimension ref="A1:T34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -31953,17 +31953,17 @@
       </c>
       <c r="R1" s="10" t="inlineStr">
         <is>
-          <t>Temuan</t>
+          <t>Findings</t>
         </is>
       </c>
       <c r="S1" s="10" t="inlineStr">
         <is>
-          <t>Tindak_Lanjut</t>
+          <t>Action_Taken</t>
         </is>
       </c>
       <c r="T1" s="10" t="inlineStr">
         <is>
-          <t>Jumlah_Foto</t>
+          <t>Photo_Count</t>
         </is>
       </c>
     </row>
@@ -33596,27 +33596,27 @@
     <row r="1" ht="24.9" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>Kategori</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="B1" s="10" t="inlineStr">
         <is>
-          <t>Nama_Equipment_Scope</t>
+          <t>Equipment_Scope_Name</t>
         </is>
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
-          <t>Tipe_Scope_Vendor_MSW</t>
+          <t>Scope_Type_Vendor_MSW</t>
         </is>
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>Scope_Kerja_ME_SI_SE</t>
+          <t>Work_Scope_ME_SI_SE</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>Deskripsi_Aktivitas</t>
+          <t>Activity_Description</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
@@ -33668,12 +33668,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pengukuran tahanan isolasi, indeks
-polarisasi (PI), winding resistance
-test, connection check,
-pemeriksaan cooler, cek sistem
-excitasi, PMG, dan kebersihan
-saluran ventilasi, grounding check</t>
+          <t>Insulation resistance measurement, polarization index (PI), winding resistance test, connection check, cooler inspection, excitation system check, PMG, ventilation duct cleaning, grounding check</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -33703,12 +33698,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pengujian tahanan isolasi, uji
-tegangan tembus, dan
-pembersihan bushing,
-pengencangan baut, dan pengujian
-fungsi proteksi, cek BDV oli trafo,
-grounding check</t>
+          <t>Insulation resistance test, breakdown voltage test, bushing cleaning, bolt retorquing, protection function test, transformer oil BDV check, grounding check</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -33738,12 +33728,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pengujian tahanan isolasi, uji
-tegangan tembus, dan
-pembersihan bushing,
-pengencangan baut, dan pengujian
-fungsi proteksi, cek BDV oli trafo,
-grounding check</t>
+          <t>Insulation resistance test, breakdown voltage test, bushing cleaning, bolt retorquing, protection function test, transformer oil BDV check, grounding check</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -33773,12 +33758,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pengujian tahanan isolasi, uji
-tegangan tembus, dan
-pembersihan bushing,
-pengencangan baut, dan pengujian
-fungsi proteksi, cek BDV oli trafo,
-grounding check</t>
+          <t>Insulation resistance test, breakdown voltage test, bushing cleaning, bolt retorquing, protection function test, transformer oil BDV check, grounding check</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -33808,12 +33788,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pengujian tahanan isolasi, uji
-tegangan tembus, dan
-pembersihan bushing,
-pengencangan baut, dan pengujian
-fungsi proteksi, cek BDV oli trafo,
-grounding check</t>
+          <t>Insulation resistance test, breakdown voltage test, bushing cleaning, bolt retorquing, protection function test, transformer oil BDV check, grounding check</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -33843,10 +33818,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Uji contact resistance pada CB, uji
-timing close-open, dan pelumasan
-mekanisme mekanis CB, grounding
-check</t>
+          <t>CB contact resistance test, close-open timing test, CB mechanical mechanism lubrication, grounding check</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -33876,10 +33848,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Uji contact resistance pada CB, uji
-timing close-open, dan pelumasan
-mekanisme mekanis CB, grounding
-check</t>
+          <t>CB contact resistance test, close-open timing test, CB mechanical mechanism lubrication, grounding check</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -33909,10 +33878,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Uji contact resistance pada CB, uji
-timing close-open, dan pelumasan
-mekanisme mekanis CB, grounding
-check</t>
+          <t>CB contact resistance test, close-open timing test, CB mechanical mechanism lubrication, grounding check</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -33942,10 +33908,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Uji contact resistance pada CB, uji
-timing close-open, dan pelumasan
-mekanisme mekanis CB, grounding
-check</t>
+          <t>CB contact resistance test, close-open timing test, CB mechanical mechanism lubrication, grounding check</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -33960,7 +33923,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Panel Generator CB 11 ME Penggantian Voltage Transformer</t>
+          <t>Generator CB Panel 11 ME Voltage Transformer Replacement</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -34125,12 +34088,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pengujian injeksi sekunder
-(Secondary Injection Test)
-untuk memastikan relay trip
-sesuai kurva waktu dan nilai
-arus settingnya, cek log
-kejadian (event recorder)</t>
+          <t>Secondary Injection Test to verify relay tripping against time curve and current setting values, event recorder log verification</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -34160,11 +34118,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Pengukuran tahanan isolasi,
-indeks polarisasi (PI),
-connection check, cek visual
-body, fan cover, dan kebersihan
-saluran ventilasi</t>
+          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -34194,11 +34148,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pengukuran tahanan isolasi,
-indeks polarisasi (PI),
-connection check, cek visual
-body, fan cover, dan kebersihan
-saluran ventilasi</t>
+          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -34213,7 +34163,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>BFP motor 2  Perbaikan leak oil bearing sisi NDE</t>
+          <t>BFP motor 2 NDE bearing oil leak repair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -34278,7 +34228,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Pengujian tahanan isolasi, kontak
+          <t>INSULATION RESISTANCE TEST, kontak
 resistan bagian konduktor,
 grounding check</t>
         </is>
@@ -34310,7 +34260,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Pengujian tahanan isolasi, kontak
+          <t>INSULATION RESISTANCE TEST, kontak
 resistan bagian konduktor,
 grounding check</t>
         </is>
@@ -34342,11 +34292,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pengukuran tahanan isolasi,
-indeks polarisasi (PI),
-connection check, cek visual
-body, fan cover, dan kebersihan
-saluran ventilasi</t>
+          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -34376,11 +34322,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Pengukuran tahanan isolasi,
-indeks polarisasi (PI),
-connection check, cek visual
-body, fan cover, dan kebersihan
-saluran ventilasi</t>
+          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and ventilation duct cleaning</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -34410,11 +34352,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Visual Inspection pada
-sambungan dan kerusakan,
-tightening &amp; cleaning,
-pengukuran grounding
-resistance dan verifikasi</t>
+          <t>Visual inspection on connections and damage, tightening &amp; cleaning, grounding resistance measurement and verification</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -34459,13 +34397,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cek kondisi fisik panel
-(kebersihan, pintu, kunci, dan
-grounding), indikator LED
-CPU/I/O/Power Supply, suhu
-panel, serta memastikan tidak
-ada alarm atau fault aktif di
-sistem.</t>
+          <t>Physical inspection of panel (cleanliness, doors, locks, grounding), CPU/I/O/Power Supply LED indicators, panel temperature, and ensuring no active alarms or system faults.</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -34495,7 +34427,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Verifikasi Dan Kalibrasi</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -34525,7 +34457,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Verifikasi Dan Kalibrasi</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -34555,7 +34487,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Verifikasi Dan Kalibrasi</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -34585,7 +34517,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Verifikasi Dan Kalibrasi</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -34632,10 +34564,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Pengukuran tahanan isolasi, indeks
-polarisasi (PI), connection check,
-cek visual body, fan cover, dan cek
-tightening terminal kabel.</t>
+          <t>Insulation resistance measurement, polarization index (PI), connection check, visual body check, fan cover, and cable terminal tightening check.</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -34665,7 +34594,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Replace Motor &amp; Gear box</t>
+          <t>Replace Motor &amp; Gearbox</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -34695,7 +34624,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Replace Motor &amp; Gear box</t>
+          <t>Replace Motor &amp; Gearbox</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -34980,7 +34909,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GENERAL INSPECTION, Add modify chute drain with Isolation Valve</t>
+          <t>GENERAL INSPECTION, modify chute drain with Isolation Valve</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -35145,7 +35074,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Replace Motor &amp; Gear box</t>
+          <t>Replace Motor &amp; Gearbox</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -35230,7 +35159,7 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>Unit 1 - GCB Panel Cooling Fan Blower rusak Mx</t>
+          <t>Unit 1 - GCB Panel Cooling Fan Blower replacement (Mx)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -35265,7 +35194,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Verifikasi &amp; Calibrasi</t>
+          <t>Verification &amp; Calibration</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -35440,7 +35369,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Verifikasi &amp; Function Test</t>
+          <t>Verification &amp; Function Test</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -35465,7 +35394,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Verifikasi &amp; Function Test</t>
+          <t>Verification &amp; Function Test</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -35485,7 +35414,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan FARHAN</t>
+          <t>Job Scope FARHAN</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -35500,7 +35429,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -35520,7 +35449,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan DEDE</t>
+          <t>Job Scope DEDE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -35535,7 +35464,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -35555,7 +35484,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan ZAINI Y</t>
+          <t>Job Scope ZAINI Y</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -35570,7 +35499,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -35590,7 +35519,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan MAJID</t>
+          <t>Job Scope MAJID</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -35605,7 +35534,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -35625,7 +35554,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan AMP</t>
+          <t>Job Scope AMP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -35640,7 +35569,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -35660,7 +35589,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan MSW</t>
+          <t>Job Scope MSW</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -35675,7 +35604,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -35695,7 +35624,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scope Pekerjaan JAPA</t>
+          <t>Job Scope JAPA</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -35710,7 +35639,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Personil EIC</t>
+          <t>EIC Personnel</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">

--- a/Template_Outage_EIC_Monitoring_unit 2.xlsx
+++ b/Template_Outage_EIC_Monitoring_unit 2.xlsx
@@ -23,11 +23,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -79,8 +80,31 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -93,8 +117,14 @@
         <bgColor rgb="FF003366"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,11 +147,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -142,6 +186,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,11 +466,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G28"/>
+  <dimension ref="B2:G35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.69140625" defaultRowHeight="14.6"/>
   <cols>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="7"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="7"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2" ht="16.3" customHeight="1">
@@ -679,6 +745,79 @@
       <c r="C28" s="5">
         <f>COUNTIF(Instrument_PressureSwitch!$R2:$R1048576,"?*")</f>
         <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="12" t="inlineStr">
+        <is>
+          <t>5. OUTAGE SCHEDULE &amp; S-CURVE PERIOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="13" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="C32" s="14" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>Outage Start Date</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Official Outage Start Baseline for S-Curve Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>Outage Finish Date</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Planned Outage Completion Baseline for S-Curve Calculation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>Target Duration (Days)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n">
+        <v>42</v>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Total planned outage overhaul window duration in calendar days</t>
+        </is>
       </c>
     </row>
   </sheetData>
